--- a/xlsx/tests/templates/weekly_timesheet.xlsx
+++ b/xlsx/tests/templates/weekly_timesheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/v0.9/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD639BB-8098-9941-8BDF-B5908317B637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B79C5CB-4A6B-EC40-B707-00C85E2D8E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5040" yWindow="-20200" windowWidth="32340" windowHeight="18380" xr2:uid="{B1B2018D-375F-FD4E-959A-2C36AF132E97}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{B1B2018D-375F-FD4E-959A-2C36AF132E97}"/>
   </bookViews>
   <sheets>
     <sheet name="Timesheet" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -130,9 +130,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -182,8 +182,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -199,6 +205,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -231,21 +243,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -254,25 +257,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -287,11 +274,36 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,631 +659,634 @@
   <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="8.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="4" customWidth="1"/>
+    <col min="1" max="2" width="8.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="7" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="6">
+      <c r="F1" s="3">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="14" cm="1">
         <f t="array" aca="1" ref="A3:A33" ca="1">F1+_xlfn.SEQUENCE(DAY(EOMONTH(F1,0)))-1</f>
-        <v>46226</v>
-      </c>
-      <c r="B3" s="9" t="str" cm="1">
+        <v>46309</v>
+      </c>
+      <c r="B3" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="B3:B33" ca="1">TEXT(_xlfn.ANCHORARRAY(A3),"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+        <v>Wed</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <f ca="1"/>
-        <v>46227</v>
-      </c>
-      <c r="B4" s="8" t="str">
-        <f ca="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+        <v>46310</v>
+      </c>
+      <c r="B4" s="17" t="str">
+        <f ca="1"/>
+        <v>Thu</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="14">
         <f ca="1"/>
-        <v>46228</v>
-      </c>
-      <c r="B5" s="8" t="str">
-        <f ca="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+        <v>46311</v>
+      </c>
+      <c r="B5" s="17" t="str">
+        <f ca="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="14">
         <f ca="1"/>
-        <v>46229</v>
-      </c>
-      <c r="B6" s="8" t="str">
-        <f ca="1"/>
-        <v>Sun</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+        <v>46312</v>
+      </c>
+      <c r="B6" s="17" t="str">
+        <f ca="1"/>
+        <v>Sat</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="14">
         <f ca="1"/>
-        <v>46230</v>
-      </c>
-      <c r="B7" s="8" t="str">
-        <f ca="1"/>
-        <v>Mon</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+        <v>46313</v>
+      </c>
+      <c r="B7" s="17" t="str">
+        <f ca="1"/>
+        <v>Sun</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <f ca="1"/>
-        <v>46231</v>
-      </c>
-      <c r="B8" s="8" t="str">
-        <f ca="1"/>
-        <v>Tue</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+        <v>46314</v>
+      </c>
+      <c r="B8" s="17" t="str">
+        <f ca="1"/>
+        <v>Mon</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="14">
         <f ca="1"/>
-        <v>46232</v>
-      </c>
-      <c r="B9" s="8" t="str">
-        <f ca="1"/>
-        <v>Wed</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+        <v>46315</v>
+      </c>
+      <c r="B9" s="17" t="str">
+        <f ca="1"/>
+        <v>Tue</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <f ca="1"/>
-        <v>46233</v>
-      </c>
-      <c r="B10" s="8" t="str">
-        <f ca="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+        <v>46316</v>
+      </c>
+      <c r="B10" s="17" t="str">
+        <f ca="1"/>
+        <v>Wed</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="14">
         <f ca="1"/>
-        <v>46234</v>
-      </c>
-      <c r="B11" s="8" t="str">
-        <f ca="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+        <v>46317</v>
+      </c>
+      <c r="B11" s="17" t="str">
+        <f ca="1"/>
+        <v>Thu</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <f ca="1"/>
-        <v>46235</v>
-      </c>
-      <c r="B12" s="8" t="str">
-        <f ca="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+        <v>46318</v>
+      </c>
+      <c r="B12" s="17" t="str">
+        <f ca="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="14">
         <f ca="1"/>
-        <v>46236</v>
-      </c>
-      <c r="B13" s="8" t="str">
-        <f ca="1"/>
-        <v>Sun</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
+        <v>46319</v>
+      </c>
+      <c r="B13" s="17" t="str">
+        <f ca="1"/>
+        <v>Sat</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="14">
         <f ca="1"/>
-        <v>46237</v>
-      </c>
-      <c r="B14" s="8" t="str">
-        <f ca="1"/>
-        <v>Mon</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+        <v>46320</v>
+      </c>
+      <c r="B14" s="17" t="str">
+        <f ca="1"/>
+        <v>Sun</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="14">
         <f ca="1"/>
-        <v>46238</v>
-      </c>
-      <c r="B15" s="8" t="str">
-        <f ca="1"/>
-        <v>Tue</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
+        <v>46321</v>
+      </c>
+      <c r="B15" s="17" t="str">
+        <f ca="1"/>
+        <v>Mon</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="14">
         <f ca="1"/>
-        <v>46239</v>
-      </c>
-      <c r="B16" s="8" t="str">
-        <f ca="1"/>
-        <v>Wed</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
+        <v>46322</v>
+      </c>
+      <c r="B16" s="17" t="str">
+        <f ca="1"/>
+        <v>Tue</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="14">
         <f ca="1"/>
-        <v>46240</v>
-      </c>
-      <c r="B17" s="8" t="str">
-        <f ca="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
+        <v>46323</v>
+      </c>
+      <c r="B17" s="17" t="str">
+        <f ca="1"/>
+        <v>Wed</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="14">
         <f ca="1"/>
-        <v>46241</v>
-      </c>
-      <c r="B18" s="8" t="str">
-        <f ca="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
+        <v>46324</v>
+      </c>
+      <c r="B18" s="17" t="str">
+        <f ca="1"/>
+        <v>Thu</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="14">
         <f ca="1"/>
-        <v>46242</v>
-      </c>
-      <c r="B19" s="8" t="str">
-        <f ca="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
+        <v>46325</v>
+      </c>
+      <c r="B19" s="17" t="str">
+        <f ca="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="14">
         <f ca="1"/>
-        <v>46243</v>
-      </c>
-      <c r="B20" s="8" t="str">
-        <f ca="1"/>
-        <v>Sun</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
+        <v>46326</v>
+      </c>
+      <c r="B20" s="17" t="str">
+        <f ca="1"/>
+        <v>Sat</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="14">
         <f ca="1"/>
-        <v>46244</v>
-      </c>
-      <c r="B21" s="8" t="str">
-        <f ca="1"/>
-        <v>Mon</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
+        <v>46327</v>
+      </c>
+      <c r="B21" s="17" t="str">
+        <f ca="1"/>
+        <v>Sun</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="14">
         <f ca="1"/>
-        <v>46245</v>
-      </c>
-      <c r="B22" s="8" t="str">
-        <f ca="1"/>
-        <v>Tue</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
+        <v>46328</v>
+      </c>
+      <c r="B22" s="17" t="str">
+        <f ca="1"/>
+        <v>Mon</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="14">
         <f ca="1"/>
-        <v>46246</v>
-      </c>
-      <c r="B23" s="8" t="str">
-        <f ca="1"/>
-        <v>Wed</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
+        <v>46329</v>
+      </c>
+      <c r="B23" s="17" t="str">
+        <f ca="1"/>
+        <v>Tue</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="14">
         <f ca="1"/>
-        <v>46247</v>
-      </c>
-      <c r="B24" s="8" t="str">
-        <f ca="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
+        <v>46330</v>
+      </c>
+      <c r="B24" s="17" t="str">
+        <f ca="1"/>
+        <v>Wed</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="14">
         <f ca="1"/>
-        <v>46248</v>
-      </c>
-      <c r="B25" s="8" t="str">
-        <f ca="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
+        <v>46331</v>
+      </c>
+      <c r="B25" s="17" t="str">
+        <f ca="1"/>
+        <v>Thu</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="14">
         <f ca="1"/>
-        <v>46249</v>
-      </c>
-      <c r="B26" s="8" t="str">
-        <f ca="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
+        <v>46332</v>
+      </c>
+      <c r="B26" s="17" t="str">
+        <f ca="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="14">
         <f ca="1"/>
-        <v>46250</v>
-      </c>
-      <c r="B27" s="8" t="str">
-        <f ca="1"/>
-        <v>Sun</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
+        <v>46333</v>
+      </c>
+      <c r="B27" s="17" t="str">
+        <f ca="1"/>
+        <v>Sat</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="14">
         <f ca="1"/>
-        <v>46251</v>
-      </c>
-      <c r="B28" s="8" t="str">
-        <f ca="1"/>
-        <v>Mon</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
+        <v>46334</v>
+      </c>
+      <c r="B28" s="17" t="str">
+        <f ca="1"/>
+        <v>Sun</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="14">
         <f ca="1"/>
-        <v>46252</v>
-      </c>
-      <c r="B29" s="8" t="str">
-        <f ca="1"/>
-        <v>Tue</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
+        <v>46335</v>
+      </c>
+      <c r="B29" s="17" t="str">
+        <f ca="1"/>
+        <v>Mon</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="14">
         <f ca="1"/>
-        <v>46253</v>
-      </c>
-      <c r="B30" s="8" t="str">
-        <f ca="1"/>
-        <v>Wed</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
+        <v>46336</v>
+      </c>
+      <c r="B30" s="17" t="str">
+        <f ca="1"/>
+        <v>Tue</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="14">
         <f ca="1"/>
-        <v>46254</v>
-      </c>
-      <c r="B31" s="8" t="str">
-        <f ca="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
+        <v>46337</v>
+      </c>
+      <c r="B31" s="17" t="str">
+        <f ca="1"/>
+        <v>Wed</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="14">
         <f ca="1"/>
-        <v>46255</v>
-      </c>
-      <c r="B32" s="8" t="str">
-        <f ca="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
+        <v>46338</v>
+      </c>
+      <c r="B32" s="17" t="str">
+        <f ca="1"/>
+        <v>Thu</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="14">
         <f ca="1"/>
-        <v>46256</v>
-      </c>
-      <c r="B33" s="8" t="str">
-        <f ca="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
+        <v>46339</v>
+      </c>
+      <c r="B33" s="17" t="str">
+        <f ca="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <conditionalFormatting sqref="A3:F33">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>WEEKDAY($A3,2)&gt;5</formula>
@@ -1287,259 +1302,262 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
+      <c r="A3" s="18">
         <f ca="1">_xlfn.ISOWEEKNUM(Timesheet!F1)</f>
-        <v>30</v>
-      </c>
-      <c r="B3" s="1" cm="1">
+        <v>42</v>
+      </c>
+      <c r="B3" s="19" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A3)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A3))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="1" cm="1">
+      <c r="C3" s="19" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A3)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A3))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="1" cm="1">
+      <c r="D3" s="19" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A3)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A3))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="E3" s="1" cm="1">
+      <c r="E3" s="19" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A3)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A3))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="1" cm="1">
+      <c r="F3" s="19" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A3)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A3))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+      <c r="A4" s="18">
         <f ca="1">A3+1</f>
-        <v>31</v>
-      </c>
-      <c r="B4" s="1" cm="1">
+        <v>43</v>
+      </c>
+      <c r="B4" s="19" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A4)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A4))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="1" cm="1">
+      <c r="C4" s="19" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A4)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A4))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="1" cm="1">
+      <c r="D4" s="19" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A4)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A4))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="1" cm="1">
+      <c r="E4" s="19" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A4)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A4))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="1" cm="1">
+      <c r="F4" s="19" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A4)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A4))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
+      <c r="A5" s="18">
         <f t="shared" ref="A5:A7" ca="1" si="0">A4+1</f>
-        <v>32</v>
-      </c>
-      <c r="B5" s="1" cm="1">
+        <v>44</v>
+      </c>
+      <c r="B5" s="19" cm="1">
         <f t="array" aca="1" ref="B5" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A5)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A5))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="1" cm="1">
+      <c r="C5" s="19" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A5)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A5))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="1" cm="1">
+      <c r="D5" s="19" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A5)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A5))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="1" cm="1">
+      <c r="E5" s="19" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A5)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A5))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="1" cm="1">
+      <c r="F5" s="19" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A5)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A5))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+      <c r="A6" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B6" s="1" cm="1">
+        <v>45</v>
+      </c>
+      <c r="B6" s="19" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A6)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A6))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="1" cm="1">
+      <c r="C6" s="19" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A6)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A6))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="1" cm="1">
+      <c r="D6" s="19" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A6)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A6))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="1" cm="1">
+      <c r="E6" s="19" cm="1">
         <f t="array" aca="1" ref="E6" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A6)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A6))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="1" cm="1">
+      <c r="F6" s="19" cm="1">
         <f t="array" aca="1" ref="F6" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A6)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A6))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+      <c r="A7" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B7" s="1" cm="1">
+        <v>46</v>
+      </c>
+      <c r="B7" s="19" cm="1">
         <f t="array" aca="1" ref="B7" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A7)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A7))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="1" cm="1">
+      <c r="C7" s="19" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A7)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A7))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="1" cm="1">
+      <c r="D7" s="19" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A7)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A7))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="1" cm="1">
+      <c r="E7" s="19" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A7)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A7))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="1" cm="1">
+      <c r="F7" s="19" cm="1">
         <f t="array" aca="1" ref="F7" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A7)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A7))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="A8" s="18">
         <f ca="1">A7+1</f>
-        <v>35</v>
-      </c>
-      <c r="B8" s="1" cm="1">
+        <v>47</v>
+      </c>
+      <c r="B8" s="19" cm="1">
         <f t="array" aca="1" ref="B8" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A8)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A8))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="1" cm="1">
+      <c r="C8" s="19" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A8)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A8))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="1" cm="1">
+      <c r="D8" s="19" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A8)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A8))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="1" cm="1">
+      <c r="E8" s="19" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A8)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A8))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="1" cm="1">
+      <c r="F8" s="19" cm="1">
         <f t="array" aca="1" ref="F8" ca="1">SUMPRODUCT((_xlfn.ISOWEEKNUM(Timesheet!$A$3:$A$33)=$A8)*(WEEKDAY(Timesheet!$A$3:$A$33,2)=COLUMN()-COLUMN($A8))*Timesheet!$E$3:$E$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="6">
         <f ca="1">SUM(B3:B8)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="6">
         <f t="shared" ref="C9:F9" ca="1" si="1">SUM(C3:C8)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="6">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="6">
         <f ca="1">SUM(E3:E8)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="6">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20">
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="11">
         <f ca="1">SUM(B9:F9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19" t="s">
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="str" cm="1">
+      <c r="A14" s="25" t="str" cm="1">
         <f t="array" ref="A14">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Timesheet!C3:C33,Timesheet!C3:C33&lt;&gt;"","No entries yet"))</f>
         <v>No entries yet</v>
       </c>
-      <c r="E14" s="1" t="str" cm="1">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="19" t="str" cm="1">
         <f t="array" ref="E14">IF(COUNTA(Timesheet!$C$3:$C$33)=0,"",SUMIF(Timesheet!$C$3:$C$33,_xlfn.ANCHORARRAY(A14),Timesheet!$E$3:$E$33))</f>
         <v/>
       </c>
@@ -1549,110 +1567,220 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E15" s="1"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E16" s="1"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="19"/>
       <c r="F16" s="21"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E17" s="1"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="21"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E18" s="1"/>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="19"/>
       <c r="F18" s="21"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E19" s="1"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="19"/>
       <c r="F19" s="21"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E20" s="1"/>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="19"/>
       <c r="F20" s="21"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E21" s="1"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E22" s="1"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="21"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E23" s="1"/>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="19"/>
       <c r="F23" s="21"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E24" s="1"/>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="19"/>
       <c r="F24" s="21"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E25" s="1"/>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E26" s="1"/>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="19"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E27" s="1"/>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="19"/>
       <c r="F27" s="21"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E28" s="1"/>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="19"/>
       <c r="F28" s="21"/>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E29" s="1"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="19"/>
       <c r="F29" s="21"/>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E30" s="1"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="19"/>
       <c r="F30" s="21"/>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E31" s="1"/>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="19"/>
       <c r="F31" s="21"/>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E32" s="1"/>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="19"/>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E33" s="1"/>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="19"/>
       <c r="F33" s="21"/>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E34" s="1"/>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="19"/>
       <c r="F34" s="21"/>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E35" s="1"/>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="19"/>
       <c r="F35" s="21"/>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E36" s="1"/>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="19"/>
       <c r="F36" s="21"/>
     </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E37" s="1"/>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="21"/>
     </row>
-    <row r="38" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E38" s="1"/>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="21"/>
     </row>
-    <row r="39" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E39" s="1"/>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="20"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="19"/>
       <c r="F39" s="21"/>
     </row>
-    <row r="40" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E40" s="1"/>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="20"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="19"/>
       <c r="F40" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:D13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1663,12 +1791,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="13">
         <f ca="1">NOW()</f>
-        <v>46226.523765162034</v>
+        <v>46309.731375578704</v>
       </c>
     </row>
   </sheetData>
